--- a/Data/MM/MM_Quizzes.xlsx
+++ b/Data/MM/MM_Quizzes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\Semester 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\MM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34C8BA6-BB1D-4AB6-A884-3D58A8F9EE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8269BC-34AC-4DFD-AE6C-BDE52FEAE379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="13" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <definedName name="ExternalData_5" localSheetId="4" hidden="1">'Week 5'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_6" localSheetId="5" hidden="1">'Week 6'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_7" localSheetId="6" hidden="1">'Week 7'!$A$1:$F$21</definedName>
-    <definedName name="ExternalData_8" localSheetId="7" hidden="1">'Week 8'!$A$1:$G$21</definedName>
+    <definedName name="ExternalData_8" localSheetId="7" hidden="1">'Week 8'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_9" localSheetId="8" hidden="1">'Week 9'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="1104">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -3392,9 +3392,6 @@
     <t>A decrease in mobile device availability</t>
   </si>
   <si>
-    <t>That’s in Revisit the videos for this week</t>
-  </si>
-  <si>
     <t>QuestionID</t>
   </si>
   <si>
@@ -3414,6 +3411,12 @@
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -3507,14 +3510,15 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{503F8634-D6F2-4FA8-8707-7DE5F362FE7D}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3522,14 +3526,15 @@
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_10" connectionId="2" xr16:uid="{6A730AB3-9D1E-4047-A078-0985D3705212}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3537,14 +3542,15 @@
 
 <file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_11" connectionId="3" xr16:uid="{986C7A6C-3BD6-4C39-848B-536EA81EDFB8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3552,14 +3558,15 @@
 
 <file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_12" connectionId="4" xr16:uid="{476219D0-CA65-461B-8126-C3E0BE721F80}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3567,7 +3574,41 @@
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="5" xr16:uid="{1C0B3174-DBA2-43C8-8C1A-01EE9E3F17EC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="8">
+  <queryTableRefresh nextId="9" unboundColumnsRight="1">
+    <queryTableFields count="8">
+      <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
+      <queryTableField id="2" name="Question" tableColumnId="2"/>
+      <queryTableField id="3" name="Option_A" tableColumnId="3"/>
+      <queryTableField id="4" name="Option_B" tableColumnId="4"/>
+      <queryTableField id="5" name="Option_C" tableColumnId="5"/>
+      <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" name="6" tableColumnId="7"/>
+      <queryTableField id="8" dataBound="0" tableColumnId="8"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="6" xr16:uid="{FBC93A36-6217-43C1-927E-DD313E2AD672}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="9" unboundColumnsRight="1">
+    <queryTableFields count="8">
+      <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
+      <queryTableField id="2" name="Question" tableColumnId="2"/>
+      <queryTableField id="3" name="Option_A" tableColumnId="3"/>
+      <queryTableField id="4" name="Option_B" tableColumnId="4"/>
+      <queryTableField id="5" name="Option_C" tableColumnId="5"/>
+      <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" name="6" tableColumnId="7"/>
+      <queryTableField id="8" dataBound="0" tableColumnId="8"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_4" connectionId="7" xr16:uid="{475F5802-C203-42B2-9CA7-A4CE17E103E5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
     <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
@@ -3575,15 +3616,15 @@
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
-      <queryTableField id="7" name="6" tableColumnId="7"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
-<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="6" xr16:uid="{FBC93A36-6217-43C1-927E-DD313E2AD672}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="8">
+<file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_5" connectionId="8" xr16:uid="{0D23E931-F8FD-4C39-99C1-EA3B8BFC89D5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
     <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
@@ -3591,37 +3632,7 @@
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
-      <queryTableField id="7" name="6" tableColumnId="7"/>
-    </queryTableFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
-<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_4" connectionId="7" xr16:uid="{475F5802-C203-42B2-9CA7-A4CE17E103E5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
-      <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
-      <queryTableField id="2" name="Question" tableColumnId="2"/>
-      <queryTableField id="3" name="Option_A" tableColumnId="3"/>
-      <queryTableField id="4" name="Option_B" tableColumnId="4"/>
-      <queryTableField id="5" name="Option_C" tableColumnId="5"/>
-      <queryTableField id="6" name="Option_D" tableColumnId="6"/>
-    </queryTableFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
-<file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_5" connectionId="8" xr16:uid="{0D23E931-F8FD-4C39-99C1-EA3B8BFC89D5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
-      <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
-      <queryTableField id="2" name="Question" tableColumnId="2"/>
-      <queryTableField id="3" name="Option_A" tableColumnId="3"/>
-      <queryTableField id="4" name="Option_B" tableColumnId="4"/>
-      <queryTableField id="5" name="Option_C" tableColumnId="5"/>
-      <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3629,14 +3640,15 @@
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_6" connectionId="9" xr16:uid="{F240C777-9AAD-4AC4-8ED4-B40068EE9AC7}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3644,14 +3656,15 @@
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_7" connectionId="10" xr16:uid="{8C8F528C-D1B5-4BB6-812C-221E98DF7940}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3659,7 +3672,7 @@
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_8" connectionId="11" xr16:uid="{8B0E5243-BB50-4BA1-AA00-5EDB9B537CE8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="8">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
     <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
@@ -3667,174 +3680,188 @@
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
-      <queryTableField id="7" name="6" tableColumnId="7"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
+    <queryTableDeletedFields count="1">
+      <deletedField name="6"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_9" connectionId="12" xr16:uid="{BB599E9E-FCC0-46DE-939C-50A68FD3433E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{108A49E5-F4C9-4BE4-81CF-985786179EB3}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{108A49E5-F4C9-4BE4-81CF-985786179EB3}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{23F28495-6D9C-49A4-B266-0E90B8B992DA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{108A49E5-F4C9-4BE4-81CF-985786179EB3}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{108A49E5-F4C9-4BE4-81CF-985786179EB3}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{23F28495-6D9C-49A4-B266-0E90B8B992DA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{280CC09A-5D0F-451C-829D-A96F15FF3FE9}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{81DBC783-E006-4DD4-A3C9-B1207E3D11C6}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7B687F97-A486-4A65-AF6C-47F656570B31}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{05749D27-12A8-4FAC-B2FB-2E08BC09E34A}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{1EF57E62-9857-4C5A-9F6C-718A52FED553}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{E2648446-9D07-4B5C-8B4B-78CCD6AA8EF9}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{736AAE8E-55D8-412E-81B6-D6954B8A6125}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{736AAE8E-55D8-412E-81B6-D6954B8A6125}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AD1EC2CD-28D1-44B6-983D-A588991A1EB9}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{736AAE8E-55D8-412E-81B6-D6954B8A6125}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{736AAE8E-55D8-412E-81B6-D6954B8A6125}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{AD1EC2CD-28D1-44B6-983D-A588991A1EB9}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{5C3B75CF-D1FB-4653-A106-88EBED75687E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{0F35A9CB-01FB-41C9-BAA0-C790B2930E13}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{B022B9F1-2395-41FF-AD44-3F05B4EDE092}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{B826EA07-FD22-48F0-A9B6-6438826081B9}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{F13A5CDA-AD17-4799-82C9-12BCBCA2DE34}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{B2755C2C-5BE2-4A6D-AF76-39AF1BE66AD3}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{115E6E93-6F6A-4148-8B26-43810E040C02}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{115E6E93-6F6A-4148-8B26-43810E040C02}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8FF5EE9F-B4A9-4FF9-90DE-1F6CBD189C36}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{115E6E93-6F6A-4148-8B26-43810E040C02}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{115E6E93-6F6A-4148-8B26-43810E040C02}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{8FF5EE9F-B4A9-4FF9-90DE-1F6CBD189C36}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{8D4242C0-7B0E-40A3-BE9C-E16D3B458D99}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{2CE60761-D676-493E-9EBB-A2AD751FD099}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{0126C7C3-08AD-40E0-ADCF-34CF386A6C65}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{DB8F7D91-64E8-42B4-AEA6-5E55F3EDE761}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{CCB34C89-0014-4673-8E1D-4CE64DE11CC6}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{C70FB267-F38A-48E4-B645-A823F1DF7A85}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{E601853D-A8CA-48D1-A7EF-DA4AF2709773}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{E601853D-A8CA-48D1-A7EF-DA4AF2709773}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{E601853D-A8CA-48D1-A7EF-DA4AF2709773}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{E601853D-A8CA-48D1-A7EF-DA4AF2709773}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{8C2BB00D-17A0-40A0-8644-8AA4196A4042}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{8609DC3B-7683-4FB2-B670-98872D19EC43}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{0ABB86A6-542C-4C98-9C05-D1E09508AA7B}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{27204BA8-1BBA-4AB2-822E-FDA88828CCEB}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{C5019955-543C-48E6-8518-A1BD04D18213}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{A7542527-A952-4319-870C-6C488C5ED38B}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{A1AD0407-F556-4CCD-928F-FD367E18E016}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{8D3779E1-02CA-48FD-8305-871EC3849830}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:G21" xr:uid="{8D3779E1-02CA-48FD-8305-871EC3849830}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{934E1CB7-6C3E-4C05-9085-A38DCBD77688}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{8D3779E1-02CA-48FD-8305-871EC3849830}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:H21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H21" xr:uid="{8D3779E1-02CA-48FD-8305-871EC3849830}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{934E1CB7-6C3E-4C05-9085-A38DCBD77688}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{088B7589-344C-4D78-A36E-2859009B91CC}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{616429C3-DBAA-4F15-8C67-AB3E965CB5E8}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{42725E6C-FDDD-4A90-9C29-A344D4161F58}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2516433E-E62F-4521-97FF-2FC31EDC0321}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{F3116CFB-1153-4957-8292-CD77F5BAB610}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{E346DAE1-5C38-4ADE-A14F-0CC7BDE72455}" uniqueName="7" name="6" queryTableFieldId="7"/>
+    <tableColumn id="8" xr3:uid="{E0C128B5-965C-40A2-9F61-468823DCF2E3}" uniqueName="8" name="Answer" queryTableFieldId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{3AA18DAC-66AF-455B-9BB6-F5DBD23BF428}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:G21" xr:uid="{3AA18DAC-66AF-455B-9BB6-F5DBD23BF428}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{23BADF87-FF20-42C5-9D03-A67966DC604C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{3AA18DAC-66AF-455B-9BB6-F5DBD23BF428}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:H21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H21" xr:uid="{3AA18DAC-66AF-455B-9BB6-F5DBD23BF428}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{23BADF87-FF20-42C5-9D03-A67966DC604C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{08DA67A6-082E-47B8-8A58-86DCFBCF7B1B}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{DF5F01A7-B6F4-4957-BFA0-4927CD649788}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{C0E699DC-7F42-44E3-9EF0-F254BA616B5D}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{389B32E4-93AF-40E6-913B-8A33F8CA8FF3}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{97CE51D6-0AC8-43D9-8B5C-B6CBCE93759B}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{8DBFDCD9-D9F5-4E9D-81D5-7386997F0252}" uniqueName="7" name="6" queryTableFieldId="7"/>
+    <tableColumn id="8" xr3:uid="{F5EF50F1-E1F2-49C7-86B9-0FFAF1DC83EC}" uniqueName="8" name="Answer" queryTableFieldId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{D42A534F-1E22-41F0-AC63-FA75A40DD7F0}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{D42A534F-1E22-41F0-AC63-FA75A40DD7F0}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7F4C833A-8B0C-470C-8375-4E851A23FAE6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{D42A534F-1E22-41F0-AC63-FA75A40DD7F0}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{D42A534F-1E22-41F0-AC63-FA75A40DD7F0}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{7F4C833A-8B0C-470C-8375-4E851A23FAE6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{00E4EA3A-98F1-4C55-9F1A-42F7049EDE8B}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{2BB44DC7-E281-4505-A979-10C2284C0DAA}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{86B68943-E336-4B8E-ACE2-7465F4B4F98F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{1F804039-371A-4055-9CBD-484FF6AE5B25}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{8D06060F-FDA8-4CD3-92E9-5BCC7A8D7CC4}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{133D3D25-179E-4874-8A56-E2B259BA49ED}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{8AC1E876-71A9-40B3-B901-CE26FD77F13C}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{8AC1E876-71A9-40B3-B901-CE26FD77F13C}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9D519E24-ACE3-4879-B22E-7F24183879F6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{8AC1E876-71A9-40B3-B901-CE26FD77F13C}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{8AC1E876-71A9-40B3-B901-CE26FD77F13C}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{9D519E24-ACE3-4879-B22E-7F24183879F6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{1E0E80D6-D2A9-4018-82D0-DAF5FBE79144}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{CF91729B-41BA-445F-AC73-19FCBCBDD10B}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{6E102DCE-6DAE-4E1C-8B66-25CABDC16D2D}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{E76F0D1E-FD5F-4EB7-8E86-0FDA30F79C7D}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{A428EEE8-7148-4B6C-B6AB-6EF7D2125B67}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{04CA1BC2-870E-4BDA-B400-7B94DA5CB723}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{0234C1D2-44FC-4B37-AE68-3B82F2ED5CA8}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{0234C1D2-44FC-4B37-AE68-3B82F2ED5CA8}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{0234C1D2-44FC-4B37-AE68-3B82F2ED5CA8}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{0234C1D2-44FC-4B37-AE68-3B82F2ED5CA8}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{BB833E3F-64C8-426A-8F3E-916B5470C0E9}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{8E53AB5A-228E-4F86-9764-A53269E8824D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{A6084BCF-8211-4260-828A-6E5216EEB3B5}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{30610351-C464-4B65-BC5F-ED3956390D2F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{A78FCD2D-2257-4ED9-A407-1CFC30C1849D}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{6B858FF1-89B9-4EF5-8876-F5D774A70281}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{43360837-A9A9-4260-AECD-6A6C252C064A}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5DAFDD33-7700-49D8-BBE9-8835C84543A8}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{5DAFDD33-7700-49D8-BBE9-8835C84543A8}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D8747363-122F-44F1-A3CE-E9B4FB7D824C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5DAFDD33-7700-49D8-BBE9-8835C84543A8}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{5DAFDD33-7700-49D8-BBE9-8835C84543A8}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{D8747363-122F-44F1-A3CE-E9B4FB7D824C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{9ADBF966-7E2C-4F1C-AA0E-29488150A89E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{58EF7605-5E9C-45F8-97D8-5EFEFDB7A1D9}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{968AC97E-D043-46EE-A3BD-C6C75BC023F1}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{C1BED39E-EEBA-47ED-990F-075AE15BDDCC}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{C80526A5-7682-43E6-943F-C59E070E25E1}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{969461A7-14DD-4DA8-8DA1-3BA5563A6080}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3844,28 +3871,29 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{FD6B295C-AF5A-4388-A39A-36F20F291A47}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{FD6B295C-AF5A-4388-A39A-36F20F291A47}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9910D7F9-4663-451A-9A42-B49E8C11DD2E}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{9910D7F9-4663-451A-9A42-B49E8C11DD2E}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{916D350A-DF56-442C-8F18-BD4F5AD488BC}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{57F78225-BF03-42CF-B560-5FCB9CED5886}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{8A4BB2E4-F1D8-41BE-A5C8-36D1F23B2B05}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{F7576F9F-9B7D-4924-B017-A3D2CB07F655}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{F6A2F866-B24B-4BE6-AB61-6A6542575F1B}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{9DF7B338-BA12-4275-86D5-54FF741D57DB}" uniqueName="7" name="6" queryTableFieldId="7"/>
+    <tableColumn id="7" xr3:uid="{9DF7B338-BA12-4275-86D5-54FF741D57DB}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{64356F33-4EFC-456D-B07D-A19E63B1040F}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{64356F33-4EFC-456D-B07D-A19E63B1040F}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{5C9979C7-C12B-411D-8179-293B69CCBAB0}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{64356F33-4EFC-456D-B07D-A19E63B1040F}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{64356F33-4EFC-456D-B07D-A19E63B1040F}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{5C9979C7-C12B-411D-8179-293B69CCBAB0}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{F0F015C2-AB89-4054-B0C1-A343FE1795CA}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{ED811945-2A91-42F7-A587-ECC4F8F09EF2}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{F48480EF-7A4C-4CFD-A6D8-35822B67332B}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{FA12F405-0603-497B-BD09-00FAD2B1E5F6}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{137AA93D-5F75-4B9A-B56D-64EEC4F3D154}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{D2614F2F-A918-459E-8ED2-70F638E6ADF1}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4189,7 +4217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7154198-EAAE-4F04-BB28-8EFA5A6974B8}">
   <sheetPr codeName="Sheet24"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4200,27 +4228,30 @@
     <col min="6" max="6" width="72.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4239,8 +4270,11 @@
       <c r="F2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4259,8 +4293,11 @@
       <c r="F3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4279,8 +4316,11 @@
       <c r="F4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4299,8 +4339,11 @@
       <c r="F5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4319,8 +4362,11 @@
       <c r="F6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4339,8 +4385,11 @@
       <c r="F7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4359,8 +4408,11 @@
       <c r="F8" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4379,8 +4431,11 @@
       <c r="F9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -4399,8 +4454,11 @@
       <c r="F10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -4419,8 +4477,11 @@
       <c r="F11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -4439,8 +4500,11 @@
       <c r="F12" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -4459,8 +4523,11 @@
       <c r="F13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -4479,8 +4546,11 @@
       <c r="F14" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -4499,8 +4569,11 @@
       <c r="F15" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -4519,8 +4592,11 @@
       <c r="F16" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -4539,8 +4615,11 @@
       <c r="F17" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -4559,8 +4638,11 @@
       <c r="F18" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -4579,8 +4661,11 @@
       <c r="F19" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -4599,8 +4684,11 @@
       <c r="F20" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -4618,6 +4706,9 @@
       </c>
       <c r="F21" t="s">
         <v>117</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -4631,7 +4722,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90882766-DDAE-4B9E-B08B-BCD1C12E1899}">
   <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4642,27 +4733,30 @@
     <col min="6" max="6" width="44.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4681,8 +4775,11 @@
       <c r="F2" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4701,8 +4798,11 @@
       <c r="F3" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4721,8 +4821,11 @@
       <c r="F4" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4741,8 +4844,11 @@
       <c r="F5" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4761,8 +4867,11 @@
       <c r="F6" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4781,8 +4890,11 @@
       <c r="F7" t="s">
         <v>858</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4801,8 +4913,11 @@
       <c r="F8" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4821,8 +4936,11 @@
       <c r="F9" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -4841,8 +4959,11 @@
       <c r="F10" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -4861,8 +4982,11 @@
       <c r="F11" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -4881,8 +5005,11 @@
       <c r="F12" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -4901,8 +5028,11 @@
       <c r="F13" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -4921,8 +5051,11 @@
       <c r="F14" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -4941,8 +5074,11 @@
       <c r="F15" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -4961,8 +5097,11 @@
       <c r="F16" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -4981,8 +5120,11 @@
       <c r="F17" t="s">
         <v>867</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -5001,8 +5143,11 @@
       <c r="F18" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -5021,8 +5166,11 @@
       <c r="F19" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -5041,8 +5189,11 @@
       <c r="F20" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -5060,6 +5211,9 @@
       </c>
       <c r="F21" t="s">
         <v>842</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -5073,7 +5227,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B320868E-0984-42D4-A5AB-AEBB5BE050FF}">
   <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5084,27 +5238,30 @@
     <col min="6" max="6" width="42.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5123,8 +5280,11 @@
       <c r="F2" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5143,8 +5303,11 @@
       <c r="F3" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5163,8 +5326,11 @@
       <c r="F4" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5183,8 +5349,11 @@
       <c r="F5" t="s">
         <v>927</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -5203,8 +5372,11 @@
       <c r="F6" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -5223,8 +5395,11 @@
       <c r="F7" t="s">
         <v>943</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -5243,8 +5418,11 @@
       <c r="F8" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -5263,8 +5441,11 @@
       <c r="F9" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -5283,8 +5464,11 @@
       <c r="F10" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -5303,8 +5487,11 @@
       <c r="F11" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -5323,8 +5510,11 @@
       <c r="F12" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -5343,8 +5533,11 @@
       <c r="F13" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -5363,8 +5556,11 @@
       <c r="F14" t="s">
         <v>974</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -5383,8 +5579,11 @@
       <c r="F15" t="s">
         <v>979</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -5403,8 +5602,11 @@
       <c r="F16" t="s">
         <v>933</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -5423,8 +5625,11 @@
       <c r="F17" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -5443,8 +5648,11 @@
       <c r="F18" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -5463,8 +5671,11 @@
       <c r="F19" t="s">
         <v>991</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -5483,8 +5694,11 @@
       <c r="F20" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -5502,6 +5716,9 @@
       </c>
       <c r="F21" t="s">
         <v>1001</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -5515,7 +5732,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B185DD2F-7CB7-4EB9-89C6-161AB1712B8C}">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5526,27 +5743,30 @@
     <col min="6" max="6" width="49.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5565,8 +5785,11 @@
       <c r="F2" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5585,8 +5808,11 @@
       <c r="F3" t="s">
         <v>1011</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5605,8 +5831,11 @@
       <c r="F4" t="s">
         <v>1016</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5625,8 +5854,11 @@
       <c r="F5" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -5645,8 +5877,11 @@
       <c r="F6" t="s">
         <v>1026</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -5665,8 +5900,11 @@
       <c r="F7" t="s">
         <v>1029</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -5685,8 +5923,11 @@
       <c r="F8" t="s">
         <v>1034</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -5705,8 +5946,11 @@
       <c r="F9" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -5725,8 +5969,11 @@
       <c r="F10" t="s">
         <v>1042</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -5745,8 +5992,11 @@
       <c r="F11" t="s">
         <v>1047</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -5765,8 +6015,11 @@
       <c r="F12" t="s">
         <v>1052</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -5785,8 +6038,11 @@
       <c r="F13" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -5805,8 +6061,11 @@
       <c r="F14" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -5825,8 +6084,11 @@
       <c r="F15" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -5845,8 +6107,11 @@
       <c r="F16" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -5865,8 +6130,11 @@
       <c r="F17" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -5885,8 +6153,11 @@
       <c r="F18" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -5905,8 +6176,11 @@
       <c r="F19" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -5925,8 +6199,11 @@
       <c r="F20" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -5944,6 +6221,9 @@
       </c>
       <c r="F21" t="s">
         <v>1094</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -5957,7 +6237,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6283E29E-CF80-40C4-A7FE-E6515A3248F5}">
   <sheetPr codeName="Sheet23"/>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5969,30 +6249,33 @@
     <col min="7" max="7" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1101</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6011,8 +6294,11 @@
       <c r="F2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6031,8 +6317,11 @@
       <c r="F3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6051,8 +6340,11 @@
       <c r="F4" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6071,8 +6363,11 @@
       <c r="F5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6091,8 +6386,11 @@
       <c r="F6" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -6111,8 +6409,11 @@
       <c r="F7" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6131,8 +6432,11 @@
       <c r="F8" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6151,8 +6455,11 @@
       <c r="F9" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6171,8 +6478,11 @@
       <c r="F10" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -6191,8 +6501,11 @@
       <c r="F11" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -6211,8 +6524,11 @@
       <c r="F12" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -6231,8 +6547,11 @@
       <c r="F13" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -6254,8 +6573,11 @@
       <c r="G14" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -6274,8 +6596,11 @@
       <c r="F15" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -6294,8 +6619,11 @@
       <c r="F16" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -6314,8 +6642,11 @@
       <c r="F17" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -6334,8 +6665,11 @@
       <c r="F18" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -6354,8 +6688,11 @@
       <c r="F19" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -6374,8 +6711,11 @@
       <c r="F20" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -6393,6 +6733,9 @@
       </c>
       <c r="F21" t="s">
         <v>145</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -6406,7 +6749,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F84DFD-5960-46A0-A4B5-FC722726624B}">
   <sheetPr codeName="Sheet22"/>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6418,30 +6761,33 @@
     <col min="7" max="7" width="51.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1101</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6460,8 +6806,11 @@
       <c r="F2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6480,8 +6829,11 @@
       <c r="F3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6500,8 +6852,11 @@
       <c r="F4" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6520,8 +6875,11 @@
       <c r="F5" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6543,8 +6901,11 @@
       <c r="G6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -6566,8 +6927,11 @@
       <c r="G7" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6589,8 +6953,11 @@
       <c r="G8" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6612,8 +6979,11 @@
       <c r="G9" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6635,8 +7005,11 @@
       <c r="G10" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -6658,8 +7031,11 @@
       <c r="G11" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -6681,8 +7057,11 @@
       <c r="G12" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -6704,8 +7083,11 @@
       <c r="G13" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -6727,8 +7109,11 @@
       <c r="G14" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -6750,8 +7135,11 @@
       <c r="G15" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -6773,8 +7161,11 @@
       <c r="G16" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -6796,8 +7187,11 @@
       <c r="G17" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -6819,8 +7213,11 @@
       <c r="G18" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -6839,8 +7236,11 @@
       <c r="F19" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -6862,8 +7262,11 @@
       <c r="G20" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -6884,6 +7287,9 @@
       </c>
       <c r="G21" t="s">
         <v>296</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -6897,7 +7303,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C2C6FD-975C-4C58-B592-69D928147005}">
   <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6908,27 +7314,30 @@
     <col min="6" max="6" width="55.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6947,8 +7356,11 @@
       <c r="F2" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6967,8 +7379,11 @@
       <c r="F3" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6987,8 +7402,11 @@
       <c r="F4" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7007,8 +7425,11 @@
       <c r="F5" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7027,8 +7448,11 @@
       <c r="F6" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7047,8 +7471,11 @@
       <c r="F7" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7067,8 +7494,11 @@
       <c r="F8" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7087,8 +7517,11 @@
       <c r="F9" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7107,8 +7540,11 @@
       <c r="F10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -7127,8 +7563,11 @@
       <c r="F11" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -7147,8 +7586,11 @@
       <c r="F12" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -7167,8 +7609,11 @@
       <c r="F13" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7187,8 +7632,11 @@
       <c r="F14" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -7207,8 +7655,11 @@
       <c r="F15" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -7227,8 +7678,11 @@
       <c r="F16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -7247,8 +7701,11 @@
       <c r="F17" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -7267,8 +7724,11 @@
       <c r="F18" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -7287,8 +7747,11 @@
       <c r="F19" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -7307,8 +7770,11 @@
       <c r="F20" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -7326,6 +7792,9 @@
       </c>
       <c r="F21" t="s">
         <v>383</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -7339,7 +7808,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0C4F36-81B1-41A5-9A13-DFA02C22292F}">
   <sheetPr codeName="Sheet20"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7350,27 +7819,30 @@
     <col min="6" max="6" width="46.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7389,8 +7861,11 @@
       <c r="F2" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7409,8 +7884,11 @@
       <c r="F3" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7429,8 +7907,11 @@
       <c r="F4" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7449,8 +7930,11 @@
       <c r="F5" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7469,8 +7953,11 @@
       <c r="F6" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7489,8 +7976,11 @@
       <c r="F7" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7509,8 +7999,11 @@
       <c r="F8" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7529,8 +8022,11 @@
       <c r="F9" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7549,8 +8045,11 @@
       <c r="F10" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -7569,8 +8068,11 @@
       <c r="F11" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -7589,8 +8091,11 @@
       <c r="F12" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -7609,8 +8114,11 @@
       <c r="F13" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7629,8 +8137,11 @@
       <c r="F14" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -7649,8 +8160,11 @@
       <c r="F15" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -7669,8 +8183,11 @@
       <c r="F16" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -7689,8 +8206,11 @@
       <c r="F17" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -7709,8 +8229,11 @@
       <c r="F18" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -7729,8 +8252,11 @@
       <c r="F19" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -7749,8 +8275,11 @@
       <c r="F20" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -7768,6 +8297,9 @@
       </c>
       <c r="F21" t="s">
         <v>466</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -7781,7 +8313,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{855BBD7B-0966-4258-8ADF-A343560616E8}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7792,27 +8324,30 @@
     <col min="6" max="6" width="51.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7831,8 +8366,11 @@
       <c r="F2" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7851,8 +8389,11 @@
       <c r="F3" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7871,8 +8412,11 @@
       <c r="F4" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7891,8 +8435,11 @@
       <c r="F5" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7911,8 +8458,11 @@
       <c r="F6" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7931,8 +8481,11 @@
       <c r="F7" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7951,8 +8504,11 @@
       <c r="F8" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7971,8 +8527,11 @@
       <c r="F9" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7991,8 +8550,11 @@
       <c r="F10" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -8011,8 +8573,11 @@
       <c r="F11" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -8031,8 +8596,11 @@
       <c r="F12" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -8051,8 +8619,11 @@
       <c r="F13" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -8071,8 +8642,11 @@
       <c r="F14" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -8091,8 +8665,11 @@
       <c r="F15" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -8111,8 +8688,11 @@
       <c r="F16" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -8131,8 +8711,11 @@
       <c r="F17" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -8151,8 +8734,11 @@
       <c r="F18" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -8171,8 +8757,11 @@
       <c r="F19" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -8191,8 +8780,11 @@
       <c r="F20" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -8210,6 +8802,9 @@
       </c>
       <c r="F21" t="s">
         <v>561</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -8223,7 +8818,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D83384-E1F4-452B-9CFD-AE3B75E0CC3D}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8234,27 +8829,30 @@
     <col min="6" max="6" width="64" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8273,8 +8871,11 @@
       <c r="F2" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8293,8 +8894,11 @@
       <c r="F3" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8313,8 +8917,11 @@
       <c r="F4" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -8333,8 +8940,11 @@
       <c r="F5" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -8353,8 +8963,11 @@
       <c r="F6" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8373,8 +8986,11 @@
       <c r="F7" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -8393,8 +9009,11 @@
       <c r="F8" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -8413,8 +9032,11 @@
       <c r="F9" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -8433,8 +9055,11 @@
       <c r="F10" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -8453,8 +9078,11 @@
       <c r="F11" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -8473,8 +9101,11 @@
       <c r="F12" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -8493,8 +9124,11 @@
       <c r="F13" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -8513,8 +9147,11 @@
       <c r="F14" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -8533,8 +9170,11 @@
       <c r="F15" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -8553,8 +9193,11 @@
       <c r="F16" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -8573,8 +9216,11 @@
       <c r="F17" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -8593,8 +9239,11 @@
       <c r="F18" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -8613,8 +9262,11 @@
       <c r="F19" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -8633,8 +9285,11 @@
       <c r="F20" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -8652,6 +9307,9 @@
       </c>
       <c r="F21" t="s">
         <v>655</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -8679,22 +9337,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1101</v>
       </c>
       <c r="G1" t="s">
         <v>1102</v>
@@ -8719,6 +9377,9 @@
       <c r="F2" t="s">
         <v>660</v>
       </c>
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -8739,6 +9400,9 @@
       <c r="F3" t="s">
         <v>665</v>
       </c>
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -8759,6 +9423,9 @@
       <c r="F4" t="s">
         <v>670</v>
       </c>
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -8779,6 +9446,9 @@
       <c r="F5" t="s">
         <v>675</v>
       </c>
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -8799,6 +9469,9 @@
       <c r="F6" t="s">
         <v>680</v>
       </c>
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -8819,6 +9492,9 @@
       <c r="F7" t="s">
         <v>685</v>
       </c>
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -8839,6 +9515,9 @@
       <c r="F8" t="s">
         <v>690</v>
       </c>
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -8859,6 +9538,9 @@
       <c r="F9" t="s">
         <v>695</v>
       </c>
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -8879,6 +9561,9 @@
       <c r="F10" t="s">
         <v>700</v>
       </c>
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -8899,6 +9584,9 @@
       <c r="F11" t="s">
         <v>705</v>
       </c>
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -8919,6 +9607,9 @@
       <c r="F12" t="s">
         <v>710</v>
       </c>
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -8940,7 +9631,7 @@
         <v>715</v>
       </c>
       <c r="G13" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8962,6 +9653,9 @@
       <c r="F14" t="s">
         <v>720</v>
       </c>
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -8983,7 +9677,7 @@
         <v>725</v>
       </c>
       <c r="G15" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9005,8 +9699,11 @@
       <c r="F16" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -9025,8 +9722,11 @@
       <c r="F17" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -9045,8 +9745,11 @@
       <c r="F18" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -9065,8 +9768,11 @@
       <c r="F19" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -9085,8 +9791,11 @@
       <c r="F20" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -9104,6 +9813,9 @@
       </c>
       <c r="F21" t="s">
         <v>754</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -9117,7 +9829,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98CCB883-28CE-4669-931D-3BA2EFC244A7}">
   <sheetPr codeName="Sheet16"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -9127,27 +9839,30 @@
     <col min="6" max="6" width="80.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1097</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1098</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1099</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1100</v>
       </c>
-      <c r="F1" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9166,8 +9881,11 @@
       <c r="F2" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -9186,8 +9904,11 @@
       <c r="F3" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -9206,8 +9927,11 @@
       <c r="F4" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -9226,8 +9950,11 @@
       <c r="F5" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -9246,8 +9973,11 @@
       <c r="F6" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -9266,8 +9996,11 @@
       <c r="F7" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -9286,8 +10019,11 @@
       <c r="F8" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -9306,8 +10042,11 @@
       <c r="F9" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -9326,8 +10065,11 @@
       <c r="F10" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -9346,8 +10088,11 @@
       <c r="F11" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -9366,8 +10111,11 @@
       <c r="F12" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -9386,8 +10134,11 @@
       <c r="F13" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -9406,8 +10157,11 @@
       <c r="F14" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -9426,8 +10180,11 @@
       <c r="F15" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -9446,8 +10203,11 @@
       <c r="F16" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -9466,8 +10226,11 @@
       <c r="F17" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -9486,8 +10249,11 @@
       <c r="F18" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -9506,8 +10272,11 @@
       <c r="F19" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -9526,8 +10295,11 @@
       <c r="F20" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -9545,6 +10317,9 @@
       </c>
       <c r="F21" t="s">
         <v>840</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>

--- a/Data/MM/MM_Quizzes.xlsx
+++ b/Data/MM/MM_Quizzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\MM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8269BC-34AC-4DFD-AE6C-BDE52FEAE379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F138A35-19FF-42D5-8176-EFBED53D2ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="13" r:id="rId1"/>
@@ -31,8 +31,8 @@
     <definedName name="ExternalData_10" localSheetId="9" hidden="1">'Week 10'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_11" localSheetId="10" hidden="1">'Week 11'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_12" localSheetId="11" hidden="1">'Week 12'!$A$1:$F$21</definedName>
-    <definedName name="ExternalData_2" localSheetId="1" hidden="1">'Week 2'!$A$1:$G$21</definedName>
-    <definedName name="ExternalData_3" localSheetId="2" hidden="1">'Week 3'!$A$1:$G$21</definedName>
+    <definedName name="ExternalData_2" localSheetId="1" hidden="1">'Week 2'!$A$1:$F$21</definedName>
+    <definedName name="ExternalData_3" localSheetId="2" hidden="1">'Week 3'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_4" localSheetId="3" hidden="1">'Week 4'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_5" localSheetId="4" hidden="1">'Week 5'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_6" localSheetId="5" hidden="1">'Week 6'!$A$1:$F$21</definedName>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="1104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1091">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -605,9 +605,6 @@
     <t>Attitude Towards Behavior</t>
   </si>
   <si>
-    <t>0.5 / 1 pts</t>
-  </si>
-  <si>
     <t>What are cognitive biases in decision-making?(Select all that apply)</t>
   </si>
   <si>
@@ -749,9 +746,6 @@
     <t>Limiting accessibility of the product</t>
   </si>
   <si>
-    <t>Neglecting customer feedback for improvement</t>
-  </si>
-  <si>
     <t>Perceived benefit or worth in exchange for the price paid</t>
   </si>
   <si>
@@ -770,9 +764,6 @@
     <t>Consistency and reliability across touchpoints</t>
   </si>
   <si>
-    <t>Creating emotional connections with customers</t>
-  </si>
-  <si>
     <t>Why is customer delight important for businesses?</t>
   </si>
   <si>
@@ -788,9 +779,6 @@
     <t>It has no impact on brand differentiation</t>
   </si>
   <si>
-    <t>It limits positive word-of-mouth</t>
-  </si>
-  <si>
     <t>Why is customer satisfaction crucial for businesses?</t>
   </si>
   <si>
@@ -803,9 +791,6 @@
     <t>It eliminates the need for product improvement</t>
   </si>
   <si>
-    <t>It leads to an increase in customer churn</t>
-  </si>
-  <si>
     <t>It drives customer loyalty and positive word-of-mouth</t>
   </si>
   <si>
@@ -824,9 +809,6 @@
     <t>Surpassing customer expectations and creating memorable experiences</t>
   </si>
   <si>
-    <t>Consistently delivering standard service</t>
-  </si>
-  <si>
     <t>Which strategy can businesses adopt to enhance customer satisfaction?</t>
   </si>
   <si>
@@ -842,9 +824,6 @@
     <t>Focusing solely on reducing product quality for cost savings</t>
   </si>
   <si>
-    <t>Limiting improvements based on customer feedback</t>
-  </si>
-  <si>
     <t>In the context of consumer value creation, what does “personalisation” primarily involve?</t>
   </si>
   <si>
@@ -878,9 +857,6 @@
     <t>Increasing the product’s price without additional benefits</t>
   </si>
   <si>
-    <t>Creating an emotional connection with customers</t>
-  </si>
-  <si>
     <t>What is a crucial aspect of measuring customer satisfaction through the Net Promoter Score (NPS)?</t>
   </si>
   <si>
@@ -896,9 +872,6 @@
     <t>Conducting surveys for feedback collection</t>
   </si>
   <si>
-    <t>Assessing the product’s quality</t>
-  </si>
-  <si>
     <t>Which of the following is a crucial aspect of value creation for consumers?</t>
   </si>
   <si>
@@ -914,9 +887,6 @@
     <t>Focusing exclusively on competitor strategies</t>
   </si>
   <si>
-    <t>Maintaining a stagnant product line</t>
-  </si>
-  <si>
     <t>What does “surprise and delight moments” in customer delight signify?</t>
   </si>
   <si>
@@ -929,9 +899,6 @@
     <t>Creating moments of surprise through unexpected gestures</t>
   </si>
   <si>
-    <t>Delivering standard services</t>
-  </si>
-  <si>
     <t>What is a crucial factor in achieving customer delight?</t>
   </si>
   <si>
@@ -941,9 +908,6 @@
     <t>Limiting the use of surprise gestures</t>
   </si>
   <si>
-    <t>Avoiding employee empowerment</t>
-  </si>
-  <si>
     <t>Which term best describes the process of value creation for consumers by businesses?</t>
   </si>
   <si>
@@ -956,9 +920,6 @@
     <t>Profit maximisation</t>
   </si>
   <si>
-    <t>Market saturation</t>
-  </si>
-  <si>
     <t>Value addition</t>
   </si>
   <si>
@@ -980,9 +941,6 @@
     <t>Limiting accessibility to premium customers</t>
   </si>
   <si>
-    <t>Offering convenience in product usage</t>
-  </si>
-  <si>
     <t>What does value creation for consumers primarily aim to achieve?</t>
   </si>
   <si>
@@ -995,9 +953,6 @@
     <t>Providing products with limited features</t>
   </si>
   <si>
-    <t>Focusing solely on increasing company profits</t>
-  </si>
-  <si>
     <t>Why is PESTEL analysis important for businesses?</t>
   </si>
   <si>
@@ -3410,13 +3365,19 @@
     <t>Option_D</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>Answer</t>
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -3575,16 +3536,18 @@
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="5" xr16:uid="{1C0B3174-DBA2-43C8-8C1A-01EE9E3F17EC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9" unboundColumnsRight="1">
-    <queryTableFields count="8">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
-      <queryTableField id="7" name="6" tableColumnId="7"/>
       <queryTableField id="8" dataBound="0" tableColumnId="8"/>
     </queryTableFields>
+    <queryTableDeletedFields count="1">
+      <deletedField name="6"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
@@ -3592,16 +3555,18 @@
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="6" xr16:uid="{FBC93A36-6217-43C1-927E-DD313E2AD672}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9" unboundColumnsRight="1">
-    <queryTableFields count="8">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
-      <queryTableField id="7" name="6" tableColumnId="7"/>
       <queryTableField id="8" dataBound="0" tableColumnId="8"/>
     </queryTableFields>
+    <queryTableDeletedFields count="1">
+      <deletedField name="6"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
@@ -3709,7 +3674,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{108A49E5-F4C9-4BE4-81CF-985786179EB3}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{108A49E5-F4C9-4BE4-81CF-985786179EB3}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{23F28495-6D9C-49A4-B266-0E90B8B992DA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{23F28495-6D9C-49A4-B266-0E90B8B992DA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{280CC09A-5D0F-451C-829D-A96F15FF3FE9}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{81DBC783-E006-4DD4-A3C9-B1207E3D11C6}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7B687F97-A486-4A65-AF6C-47F656570B31}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3725,7 +3690,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{736AAE8E-55D8-412E-81B6-D6954B8A6125}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{736AAE8E-55D8-412E-81B6-D6954B8A6125}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AD1EC2CD-28D1-44B6-983D-A588991A1EB9}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{AD1EC2CD-28D1-44B6-983D-A588991A1EB9}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{5C3B75CF-D1FB-4653-A106-88EBED75687E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{0F35A9CB-01FB-41C9-BAA0-C790B2930E13}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{B022B9F1-2395-41FF-AD44-3F05B4EDE092}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3741,7 +3706,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{115E6E93-6F6A-4148-8B26-43810E040C02}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{115E6E93-6F6A-4148-8B26-43810E040C02}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8FF5EE9F-B4A9-4FF9-90DE-1F6CBD189C36}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8FF5EE9F-B4A9-4FF9-90DE-1F6CBD189C36}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{8D4242C0-7B0E-40A3-BE9C-E16D3B458D99}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{2CE60761-D676-493E-9EBB-A2AD751FD099}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{0126C7C3-08AD-40E0-ADCF-34CF386A6C65}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3757,7 +3722,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{E601853D-A8CA-48D1-A7EF-DA4AF2709773}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{E601853D-A8CA-48D1-A7EF-DA4AF2709773}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8C2BB00D-17A0-40A0-8644-8AA4196A4042}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8C2BB00D-17A0-40A0-8644-8AA4196A4042}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{8609DC3B-7683-4FB2-B670-98872D19EC43}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{0ABB86A6-542C-4C98-9C05-D1E09508AA7B}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{27204BA8-1BBA-4AB2-822E-FDA88828CCEB}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3770,16 +3735,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{8D3779E1-02CA-48FD-8305-871EC3849830}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:H21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H21" xr:uid="{8D3779E1-02CA-48FD-8305-871EC3849830}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{934E1CB7-6C3E-4C05-9085-A38DCBD77688}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{8D3779E1-02CA-48FD-8305-871EC3849830}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{8D3779E1-02CA-48FD-8305-871EC3849830}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{934E1CB7-6C3E-4C05-9085-A38DCBD77688}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{088B7589-344C-4D78-A36E-2859009B91CC}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{616429C3-DBAA-4F15-8C67-AB3E965CB5E8}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{42725E6C-FDDD-4A90-9C29-A344D4161F58}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2516433E-E62F-4521-97FF-2FC31EDC0321}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{F3116CFB-1153-4957-8292-CD77F5BAB610}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{E346DAE1-5C38-4ADE-A14F-0CC7BDE72455}" uniqueName="7" name="6" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{E0C128B5-965C-40A2-9F61-468823DCF2E3}" uniqueName="8" name="Answer" queryTableFieldId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3787,16 +3751,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{3AA18DAC-66AF-455B-9BB6-F5DBD23BF428}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:H21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H21" xr:uid="{3AA18DAC-66AF-455B-9BB6-F5DBD23BF428}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{23BADF87-FF20-42C5-9D03-A67966DC604C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{3AA18DAC-66AF-455B-9BB6-F5DBD23BF428}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{3AA18DAC-66AF-455B-9BB6-F5DBD23BF428}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{23BADF87-FF20-42C5-9D03-A67966DC604C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{08DA67A6-082E-47B8-8A58-86DCFBCF7B1B}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{DF5F01A7-B6F4-4957-BFA0-4927CD649788}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{C0E699DC-7F42-44E3-9EF0-F254BA616B5D}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{389B32E4-93AF-40E6-913B-8A33F8CA8FF3}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{97CE51D6-0AC8-43D9-8B5C-B6CBCE93759B}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{8DBFDCD9-D9F5-4E9D-81D5-7386997F0252}" uniqueName="7" name="6" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{F5EF50F1-E1F2-49C7-86B9-0FFAF1DC83EC}" uniqueName="8" name="Answer" queryTableFieldId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3807,7 +3770,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{D42A534F-1E22-41F0-AC63-FA75A40DD7F0}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{D42A534F-1E22-41F0-AC63-FA75A40DD7F0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{7F4C833A-8B0C-470C-8375-4E851A23FAE6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{7F4C833A-8B0C-470C-8375-4E851A23FAE6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{00E4EA3A-98F1-4C55-9F1A-42F7049EDE8B}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{2BB44DC7-E281-4505-A979-10C2284C0DAA}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{86B68943-E336-4B8E-ACE2-7465F4B4F98F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3823,7 +3786,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{8AC1E876-71A9-40B3-B901-CE26FD77F13C}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{8AC1E876-71A9-40B3-B901-CE26FD77F13C}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9D519E24-ACE3-4879-B22E-7F24183879F6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{9D519E24-ACE3-4879-B22E-7F24183879F6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{1E0E80D6-D2A9-4018-82D0-DAF5FBE79144}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{CF91729B-41BA-445F-AC73-19FCBCBDD10B}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{6E102DCE-6DAE-4E1C-8B66-25CABDC16D2D}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3839,7 +3802,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{0234C1D2-44FC-4B37-AE68-3B82F2ED5CA8}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{0234C1D2-44FC-4B37-AE68-3B82F2ED5CA8}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BB833E3F-64C8-426A-8F3E-916B5470C0E9}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{BB833E3F-64C8-426A-8F3E-916B5470C0E9}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{8E53AB5A-228E-4F86-9764-A53269E8824D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{A6084BCF-8211-4260-828A-6E5216EEB3B5}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{30610351-C464-4B65-BC5F-ED3956390D2F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3855,7 +3818,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5DAFDD33-7700-49D8-BBE9-8835C84543A8}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{5DAFDD33-7700-49D8-BBE9-8835C84543A8}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D8747363-122F-44F1-A3CE-E9B4FB7D824C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{D8747363-122F-44F1-A3CE-E9B4FB7D824C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{9ADBF966-7E2C-4F1C-AA0E-29488150A89E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{58EF7605-5E9C-45F8-97D8-5EFEFDB7A1D9}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{968AC97E-D043-46EE-A3BD-C6C75BC023F1}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3871,7 +3834,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{FD6B295C-AF5A-4388-A39A-36F20F291A47}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{FD6B295C-AF5A-4388-A39A-36F20F291A47}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9910D7F9-4663-451A-9A42-B49E8C11DD2E}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{9910D7F9-4663-451A-9A42-B49E8C11DD2E}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{916D350A-DF56-442C-8F18-BD4F5AD488BC}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{57F78225-BF03-42CF-B560-5FCB9CED5886}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{8A4BB2E4-F1D8-41BE-A5C8-36D1F23B2B05}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3887,7 +3850,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{64356F33-4EFC-456D-B07D-A19E63B1040F}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{64356F33-4EFC-456D-B07D-A19E63B1040F}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5C9979C7-C12B-411D-8179-293B69CCBAB0}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{5C9979C7-C12B-411D-8179-293B69CCBAB0}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{F0F015C2-AB89-4054-B0C1-A343FE1795CA}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{ED811945-2A91-42F7-A587-ECC4F8F09EF2}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{F48480EF-7A4C-4CFD-A6D8-35822B67332B}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -4230,25 +4193,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4271,7 +4234,7 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4294,7 +4257,7 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4317,7 +4280,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4340,7 +4303,7 @@
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4363,7 +4326,7 @@
         <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4386,7 +4349,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4409,7 +4372,7 @@
         <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4432,7 +4395,7 @@
         <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4455,7 +4418,7 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4478,7 +4441,7 @@
         <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4501,7 +4464,7 @@
         <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4524,7 +4487,7 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4547,7 +4510,7 @@
         <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4570,7 +4533,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4593,7 +4556,7 @@
         <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4616,7 +4579,7 @@
         <v>93</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4639,7 +4602,7 @@
         <v>99</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4662,7 +4625,7 @@
         <v>105</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4685,7 +4648,7 @@
         <v>111</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4708,7 +4671,7 @@
         <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
   </sheetData>
@@ -4735,25 +4698,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4761,22 +4724,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>841</v>
+        <v>826</v>
       </c>
       <c r="C2" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="D2" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="E2" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="F2" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4784,22 +4747,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
       <c r="C3" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="D3" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="E3" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="F3" t="s">
-        <v>850</v>
+        <v>835</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4807,22 +4770,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>851</v>
+        <v>836</v>
       </c>
       <c r="C4" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="D4" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="E4" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
       <c r="F4" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4830,22 +4793,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="C5" t="s">
-        <v>857</v>
+        <v>842</v>
       </c>
       <c r="D5" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="E5" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="F5" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4853,22 +4816,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="C6" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="D6" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="E6" t="s">
-        <v>864</v>
+        <v>849</v>
       </c>
       <c r="F6" t="s">
-        <v>865</v>
+        <v>850</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4876,22 +4839,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>866</v>
+        <v>851</v>
       </c>
       <c r="C7" t="s">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="D7" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="E7" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="F7" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4899,22 +4862,22 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>869</v>
+        <v>854</v>
       </c>
       <c r="C8" t="s">
-        <v>870</v>
+        <v>855</v>
       </c>
       <c r="D8" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="E8" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F8" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4922,22 +4885,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>873</v>
+        <v>858</v>
       </c>
       <c r="C9" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="D9" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="E9" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="F9" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4945,22 +4908,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="C10" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="D10" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="E10" t="s">
-        <v>878</v>
+        <v>863</v>
       </c>
       <c r="F10" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4968,22 +4931,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="C11" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="D11" t="s">
-        <v>882</v>
+        <v>867</v>
       </c>
       <c r="E11" t="s">
-        <v>883</v>
+        <v>868</v>
       </c>
       <c r="F11" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4991,22 +4954,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>885</v>
+        <v>870</v>
       </c>
       <c r="C12" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="D12" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="E12" t="s">
-        <v>878</v>
+        <v>863</v>
       </c>
       <c r="F12" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5014,22 +4977,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="C13" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="D13" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="E13" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="F13" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5037,22 +5000,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="C14" t="s">
-        <v>891</v>
+        <v>876</v>
       </c>
       <c r="D14" t="s">
-        <v>892</v>
+        <v>877</v>
       </c>
       <c r="E14" t="s">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="F14" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5060,22 +5023,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>895</v>
+        <v>880</v>
       </c>
       <c r="C15" t="s">
-        <v>896</v>
+        <v>881</v>
       </c>
       <c r="D15" t="s">
-        <v>897</v>
+        <v>882</v>
       </c>
       <c r="E15" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="F15" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5083,22 +5046,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="C16" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="D16" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
       <c r="E16" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="F16" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5106,22 +5069,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>901</v>
+        <v>886</v>
       </c>
       <c r="C17" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="D17" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="E17" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="F17" t="s">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5129,22 +5092,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>902</v>
+        <v>887</v>
       </c>
       <c r="C18" t="s">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="D18" t="s">
-        <v>904</v>
+        <v>889</v>
       </c>
       <c r="E18" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="F18" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5152,22 +5115,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="C19" t="s">
-        <v>908</v>
+        <v>893</v>
       </c>
       <c r="D19" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="E19" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="F19" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5175,22 +5138,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="C20" t="s">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="D20" t="s">
-        <v>892</v>
+        <v>877</v>
       </c>
       <c r="E20" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="F20" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5198,22 +5161,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="C21" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="D21" t="s">
-        <v>883</v>
+        <v>868</v>
       </c>
       <c r="E21" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="F21" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
   </sheetData>
@@ -5240,25 +5203,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5266,22 +5229,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="C2" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="D2" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
       <c r="E2" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="F2" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5289,22 +5252,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="C3" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
       <c r="D3" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="E3" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="F3" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5312,22 +5275,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="C4" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="D4" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="E4" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
       <c r="F4" t="s">
-        <v>929</v>
+        <v>914</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5335,22 +5298,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>930</v>
+        <v>915</v>
       </c>
       <c r="C5" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="D5" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E5" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
       <c r="F5" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5358,22 +5321,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>934</v>
+        <v>919</v>
       </c>
       <c r="C6" t="s">
-        <v>935</v>
+        <v>920</v>
       </c>
       <c r="D6" t="s">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="E6" t="s">
-        <v>937</v>
+        <v>922</v>
       </c>
       <c r="F6" t="s">
-        <v>938</v>
+        <v>923</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5381,22 +5344,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
       <c r="C7" t="s">
-        <v>940</v>
+        <v>925</v>
       </c>
       <c r="D7" t="s">
-        <v>941</v>
+        <v>926</v>
       </c>
       <c r="E7" t="s">
-        <v>942</v>
+        <v>927</v>
       </c>
       <c r="F7" t="s">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5404,22 +5367,22 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>944</v>
+        <v>929</v>
       </c>
       <c r="C8" t="s">
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="D8" t="s">
-        <v>946</v>
+        <v>931</v>
       </c>
       <c r="E8" t="s">
-        <v>938</v>
+        <v>923</v>
       </c>
       <c r="F8" t="s">
-        <v>947</v>
+        <v>932</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5427,22 +5390,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>948</v>
+        <v>933</v>
       </c>
       <c r="C9" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="D9" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="E9" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="F9" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5450,22 +5413,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
       <c r="C10" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="D10" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
       <c r="E10" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="F10" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5473,22 +5436,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="C11" t="s">
-        <v>956</v>
+        <v>941</v>
       </c>
       <c r="D11" t="s">
-        <v>957</v>
+        <v>942</v>
       </c>
       <c r="E11" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
       <c r="F11" t="s">
-        <v>959</v>
+        <v>944</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5496,22 +5459,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="C12" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="D12" t="s">
-        <v>962</v>
+        <v>947</v>
       </c>
       <c r="E12" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="F12" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5519,22 +5482,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="C13" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="D13" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
       <c r="E13" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
       <c r="F13" t="s">
-        <v>969</v>
+        <v>954</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5542,22 +5505,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>970</v>
+        <v>955</v>
       </c>
       <c r="C14" t="s">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="D14" t="s">
-        <v>972</v>
+        <v>957</v>
       </c>
       <c r="E14" t="s">
-        <v>973</v>
+        <v>958</v>
       </c>
       <c r="F14" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5565,22 +5528,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>975</v>
+        <v>960</v>
       </c>
       <c r="C15" t="s">
-        <v>976</v>
+        <v>961</v>
       </c>
       <c r="D15" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="E15" t="s">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="F15" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5588,22 +5551,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="C16" t="s">
-        <v>981</v>
+        <v>966</v>
       </c>
       <c r="D16" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="E16" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="F16" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5611,22 +5574,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="C17" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="D17" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="E17" t="s">
-        <v>929</v>
+        <v>914</v>
       </c>
       <c r="F17" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5634,22 +5597,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="C18" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
       <c r="D18" t="s">
-        <v>986</v>
+        <v>971</v>
       </c>
       <c r="E18" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="F18" t="s">
-        <v>987</v>
+        <v>972</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5657,22 +5620,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>988</v>
+        <v>973</v>
       </c>
       <c r="C19" t="s">
-        <v>989</v>
+        <v>974</v>
       </c>
       <c r="D19" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
       <c r="E19" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5680,22 +5643,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>992</v>
+        <v>977</v>
       </c>
       <c r="C20" t="s">
-        <v>993</v>
+        <v>978</v>
       </c>
       <c r="D20" t="s">
-        <v>994</v>
+        <v>979</v>
       </c>
       <c r="E20" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="F20" t="s">
-        <v>996</v>
+        <v>981</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5703,22 +5666,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
       <c r="C21" t="s">
-        <v>998</v>
+        <v>983</v>
       </c>
       <c r="D21" t="s">
-        <v>999</v>
+        <v>984</v>
       </c>
       <c r="E21" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="F21" t="s">
-        <v>1001</v>
+        <v>986</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
   </sheetData>
@@ -5745,25 +5708,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5771,22 +5734,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="C2" t="s">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="D2" t="s">
-        <v>1004</v>
+        <v>989</v>
       </c>
       <c r="E2" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="F2" t="s">
-        <v>1006</v>
+        <v>991</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5794,22 +5757,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>1007</v>
+        <v>992</v>
       </c>
       <c r="C3" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="D3" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="E3" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="F3" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5817,22 +5780,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>1012</v>
+        <v>997</v>
       </c>
       <c r="C4" t="s">
-        <v>1013</v>
+        <v>998</v>
       </c>
       <c r="D4" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="E4" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5840,22 +5803,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="D5" t="s">
-        <v>1019</v>
+        <v>1004</v>
       </c>
       <c r="E5" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="F5" t="s">
-        <v>1021</v>
+        <v>1006</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5863,22 +5826,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>1022</v>
+        <v>1007</v>
       </c>
       <c r="C6" t="s">
-        <v>1023</v>
+        <v>1008</v>
       </c>
       <c r="D6" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="E6" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="F6" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5886,22 +5849,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="C7" t="s">
-        <v>1019</v>
+        <v>1004</v>
       </c>
       <c r="D7" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="E7" t="s">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="F7" t="s">
-        <v>1029</v>
+        <v>1014</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5909,22 +5872,22 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="C8" t="s">
-        <v>1031</v>
+        <v>1016</v>
       </c>
       <c r="D8" t="s">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="E8" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="F8" t="s">
-        <v>1034</v>
+        <v>1019</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5932,22 +5895,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="C9" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="D9" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="E9" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="F9" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5955,22 +5918,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="C10" t="s">
-        <v>1040</v>
+        <v>1025</v>
       </c>
       <c r="D10" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="E10" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="F10" t="s">
-        <v>1042</v>
+        <v>1027</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5978,22 +5941,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="C11" t="s">
-        <v>1044</v>
+        <v>1029</v>
       </c>
       <c r="D11" t="s">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="E11" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="F11" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6001,22 +5964,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="C12" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="D12" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="E12" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="F12" t="s">
-        <v>1052</v>
+        <v>1037</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6024,22 +5987,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="C13" t="s">
-        <v>1054</v>
+        <v>1039</v>
       </c>
       <c r="D13" t="s">
-        <v>1055</v>
+        <v>1040</v>
       </c>
       <c r="E13" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
       <c r="F13" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6047,22 +6010,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="C14" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="D14" t="s">
-        <v>1060</v>
+        <v>1045</v>
       </c>
       <c r="E14" t="s">
-        <v>1061</v>
+        <v>1046</v>
       </c>
       <c r="F14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6070,22 +6033,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="C15" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="D15" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="E15" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="F15" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6093,22 +6056,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>1068</v>
+        <v>1053</v>
       </c>
       <c r="C16" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="D16" t="s">
-        <v>1069</v>
+        <v>1054</v>
       </c>
       <c r="E16" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F16" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6116,22 +6079,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>1072</v>
+        <v>1057</v>
       </c>
       <c r="C17" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="D17" t="s">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="E17" t="s">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="F17" t="s">
-        <v>1076</v>
+        <v>1061</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6139,22 +6102,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>1077</v>
+        <v>1062</v>
       </c>
       <c r="C18" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="D18" t="s">
-        <v>1078</v>
+        <v>1063</v>
       </c>
       <c r="E18" t="s">
-        <v>1079</v>
+        <v>1064</v>
       </c>
       <c r="F18" t="s">
-        <v>1080</v>
+        <v>1065</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -6162,22 +6125,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>1081</v>
+        <v>1066</v>
       </c>
       <c r="C19" t="s">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="D19" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="E19" t="s">
-        <v>1083</v>
+        <v>1068</v>
       </c>
       <c r="F19" t="s">
-        <v>1084</v>
+        <v>1069</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6185,22 +6148,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>1085</v>
+        <v>1070</v>
       </c>
       <c r="C20" t="s">
-        <v>1086</v>
+        <v>1071</v>
       </c>
       <c r="D20" t="s">
-        <v>1087</v>
+        <v>1072</v>
       </c>
       <c r="E20" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="F20" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G20" t="s">
         <v>1089</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6208,22 +6171,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
       <c r="C21" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
       <c r="D21" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="E21" t="s">
-        <v>1093</v>
+        <v>1078</v>
       </c>
       <c r="F21" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
   </sheetData>
@@ -6237,7 +6200,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6283E29E-CF80-40C4-A7FE-E6515A3248F5}">
   <sheetPr codeName="Sheet23"/>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6246,36 +6209,32 @@
     <col min="4" max="4" width="77.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="81.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="74.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6294,11 +6253,11 @@
       <c r="F2" t="s">
         <v>122</v>
       </c>
-      <c r="H2" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6317,11 +6276,11 @@
       <c r="F3" t="s">
         <v>127</v>
       </c>
-      <c r="H3" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6340,11 +6299,11 @@
       <c r="F4" t="s">
         <v>132</v>
       </c>
-      <c r="H4" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6363,11 +6322,11 @@
       <c r="F5" t="s">
         <v>137</v>
       </c>
-      <c r="H5" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6386,11 +6345,11 @@
       <c r="F6" t="s">
         <v>142</v>
       </c>
-      <c r="H6" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -6409,11 +6368,11 @@
       <c r="F7" t="s">
         <v>141</v>
       </c>
-      <c r="H7" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6432,11 +6391,11 @@
       <c r="F8" t="s">
         <v>144</v>
       </c>
-      <c r="H8" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6455,11 +6414,11 @@
       <c r="F9" t="s">
         <v>151</v>
       </c>
-      <c r="H9" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6478,11 +6437,11 @@
       <c r="F10" t="s">
         <v>156</v>
       </c>
-      <c r="H10" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -6501,11 +6460,11 @@
       <c r="F11" t="s">
         <v>161</v>
       </c>
-      <c r="H11" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -6524,11 +6483,11 @@
       <c r="F12" t="s">
         <v>129</v>
       </c>
-      <c r="H12" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -6547,11 +6506,11 @@
       <c r="F13" t="s">
         <v>165</v>
       </c>
-      <c r="H13" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -6571,41 +6530,38 @@
         <v>170</v>
       </c>
       <c r="G14" t="s">
-        <v>171</v>
-      </c>
-      <c r="H14" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
       <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
         <v>172</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>173</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>174</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>175</v>
       </c>
-      <c r="F15" t="s">
-        <v>176</v>
-      </c>
-      <c r="H15" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C16" t="s">
         <v>140</v>
@@ -6619,85 +6575,85 @@
       <c r="F16" t="s">
         <v>142</v>
       </c>
-      <c r="H16" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
       <c r="B17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" t="s">
         <v>178</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>179</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>180</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>181</v>
       </c>
-      <c r="F17" t="s">
-        <v>182</v>
-      </c>
-      <c r="H17" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C18" t="s">
         <v>132</v>
       </c>
       <c r="D18" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" t="s">
         <v>184</v>
-      </c>
-      <c r="E18" t="s">
-        <v>185</v>
       </c>
       <c r="F18" t="s">
         <v>163</v>
       </c>
-      <c r="H18" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
       <c r="B19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" t="s">
         <v>186</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>187</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>188</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>189</v>
       </c>
-      <c r="F19" t="s">
-        <v>190</v>
-      </c>
-      <c r="H19" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s">
         <v>145</v>
@@ -6711,31 +6667,31 @@
       <c r="F20" t="s">
         <v>144</v>
       </c>
-      <c r="H20" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C21" t="s">
         <v>141</v>
       </c>
       <c r="D21" t="s">
+        <v>192</v>
+      </c>
+      <c r="E21" t="s">
         <v>193</v>
-      </c>
-      <c r="E21" t="s">
-        <v>194</v>
       </c>
       <c r="F21" t="s">
         <v>145</v>
       </c>
-      <c r="H21" t="s">
-        <v>1103</v>
+      <c r="G21" t="s">
+        <v>1088</v>
       </c>
     </row>
   </sheetData>
@@ -6749,7 +6705,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F84DFD-5960-46A0-A4B5-FC722726624B}">
   <sheetPr codeName="Sheet22"/>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6758,538 +6714,489 @@
     <col min="4" max="4" width="55.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="65.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="51.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" t="s">
         <v>195</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>196</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>197</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>198</v>
       </c>
-      <c r="F2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" t="s">
         <v>200</v>
       </c>
-      <c r="C3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>201</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>202</v>
       </c>
-      <c r="F3" t="s">
-        <v>203</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" t="s">
         <v>204</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>205</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>206</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>207</v>
       </c>
-      <c r="F4" t="s">
-        <v>208</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" t="s">
         <v>201</v>
       </c>
-      <c r="E5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F5" t="s">
-        <v>202</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
       <c r="B6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" t="s">
         <v>210</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>211</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>212</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>213</v>
       </c>
-      <c r="F6" t="s">
-        <v>214</v>
-      </c>
       <c r="G6" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" t="s">
         <v>216</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>217</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>218</v>
       </c>
-      <c r="E7" t="s">
-        <v>219</v>
-      </c>
-      <c r="F7" t="s">
-        <v>220</v>
-      </c>
       <c r="G7" t="s">
-        <v>221</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" t="s">
         <v>222</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>223</v>
       </c>
-      <c r="D8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E8" t="s">
-        <v>225</v>
-      </c>
-      <c r="F8" t="s">
-        <v>226</v>
-      </c>
       <c r="G8" t="s">
-        <v>227</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
       <c r="B9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F9" t="s">
         <v>228</v>
       </c>
-      <c r="C9" t="s">
-        <v>229</v>
-      </c>
-      <c r="D9" t="s">
-        <v>230</v>
-      </c>
-      <c r="E9" t="s">
-        <v>231</v>
-      </c>
-      <c r="F9" t="s">
-        <v>232</v>
-      </c>
       <c r="G9" t="s">
-        <v>233</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C10" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D10" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F10" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G10" t="s">
-        <v>239</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D11" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E11" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F11" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G11" t="s">
-        <v>245</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C12" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D12" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F12" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G12" t="s">
-        <v>251</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D13" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E13" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F13" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="G13" t="s">
-        <v>257</v>
-      </c>
-      <c r="H13" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="F14" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G14" t="s">
-        <v>263</v>
-      </c>
-      <c r="H14" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C15" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D15" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="E15" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="F15" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="G15" t="s">
-        <v>269</v>
-      </c>
-      <c r="H15" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C16" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="E16" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F16" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="G16" t="s">
-        <v>274</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D17" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="E17" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="F17" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="G17" t="s">
-        <v>278</v>
-      </c>
-      <c r="H17" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C18" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="E18" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="F18" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="G18" t="s">
-        <v>284</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
-      </c>
-      <c r="H19" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="C20" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="E20" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="F20" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="G20" t="s">
-        <v>291</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="C21" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D21" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="E21" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="F21" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="G21" t="s">
-        <v>296</v>
-      </c>
-      <c r="H21" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
   </sheetData>
@@ -7316,25 +7223,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -7342,22 +7249,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="D2" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="F2" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7365,22 +7272,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E3" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="F3" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7388,22 +7295,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="C4" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="D4" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="E4" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="F4" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7411,22 +7318,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="D5" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="E5" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="F5" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7434,22 +7341,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="C6" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="D6" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="E6" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="F6" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7457,22 +7364,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="D7" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="E7" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="F7" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7480,10 +7387,10 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C8" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="D8" t="s">
         <v>163</v>
@@ -7492,10 +7399,10 @@
         <v>132</v>
       </c>
       <c r="F8" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7503,22 +7410,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="C9" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="D9" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E9" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="F9" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7526,22 +7433,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C10" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="D10" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E10" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7549,22 +7456,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C11" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="E11" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="F11" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7572,22 +7479,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C12" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D12" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="E12" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="F12" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7595,22 +7502,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="C13" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="D13" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="E13" t="s">
         <v>163</v>
       </c>
       <c r="F13" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7618,22 +7525,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="C14" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="D14" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="E14" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F14" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7641,22 +7548,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="C15" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D15" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="E15" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="F15" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7664,22 +7571,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C16" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D16" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="E16" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7687,22 +7594,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C17" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="F17" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7710,22 +7617,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C18" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D18" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="E18" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="F18" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7733,22 +7640,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="C19" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D19" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="E19" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="F19" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7756,22 +7663,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D20" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="E20" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="F20" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7779,22 +7686,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="C21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D21" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="E21" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="F21" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
   </sheetData>
@@ -7821,25 +7728,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -7847,22 +7754,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="C2" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D2" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="E2" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="F2" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7870,22 +7777,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="C3" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="D3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="E3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="F3" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7893,22 +7800,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="E4" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="F4" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7916,22 +7823,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C5" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="D5" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="E5" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="F5" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7939,22 +7846,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="C6" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="D6" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="E6" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="F6" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7962,22 +7869,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C7" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D7" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="E7" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="F7" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7985,22 +7892,22 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C8" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="D8" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="E8" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="F8" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8008,22 +7915,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C9" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="D9" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="E9" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="F9" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8031,22 +7938,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="C10" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="D10" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="E10" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="F10" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8054,22 +7961,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="C11" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="D11" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="E11" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="F11" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8077,22 +7984,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="C12" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="D12" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="E12" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="F12" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8100,22 +8007,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="F13" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8123,22 +8030,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C14" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="D14" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E14" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="F14" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8146,22 +8053,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="C15" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="D15" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="E15" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="F15" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8169,22 +8076,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="C16" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="D16" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="E16" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="F16" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8192,22 +8099,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="D17" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="E17" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="F17" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8215,22 +8122,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C18" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="D18" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="E18" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="F18" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8238,22 +8145,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="C19" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D19" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="E19" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="F19" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8261,22 +8168,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="C20" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="D20" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="E20" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="F20" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8284,22 +8191,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="C21" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="D21" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="E21" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="F21" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
   </sheetData>
@@ -8326,25 +8233,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -8352,22 +8259,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C2" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="D2" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="E2" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="F2" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8375,22 +8282,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="C3" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="D3" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="E3" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="F3" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8398,22 +8305,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="C4" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="D4" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="E4" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="F4" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8421,22 +8328,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="C5" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="D5" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="E5" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="F5" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8444,22 +8351,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="C6" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="D6" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="E6" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="F6" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8467,22 +8374,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C7" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="D7" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="E7" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="F7" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8490,22 +8397,22 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="C8" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="D8" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="E8" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="F8" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8513,22 +8420,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="C9" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="D9" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="E9" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="F9" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8536,22 +8443,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="C10" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="D10" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="E10" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="F10" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8559,22 +8466,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="D11" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="E11" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="F11" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8582,22 +8489,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="C12" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="D12" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="E12" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="F12" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8605,22 +8512,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="C13" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="D13" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="E13" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="F13" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8628,22 +8535,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="C14" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="D14" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="E14" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="F14" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8651,22 +8558,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="C15" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="D15" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="E15" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="F15" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8674,22 +8581,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="C16" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="D16" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="E16" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="F16" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8697,22 +8604,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="C17" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D17" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="E17" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="F17" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8720,22 +8627,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="C18" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="D18" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="E18" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="F18" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8743,22 +8650,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="C19" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="D19" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="E19" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="F19" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8766,22 +8673,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="C20" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="D20" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="E20" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="F20" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8789,22 +8696,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="C21" t="s">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="D21" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="E21" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="F21" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
   </sheetData>
@@ -8831,25 +8738,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -8857,22 +8764,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="C2" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="D2" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="E2" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="F2" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8880,22 +8787,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="C3" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="D3" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="E3" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F3" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8903,22 +8810,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="C4" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="D4" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="E4" t="s">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="F4" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8926,22 +8833,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="C5" t="s">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="D5" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="E5" t="s">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="F5" t="s">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8949,22 +8856,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="C6" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="D6" t="s">
-        <v>584</v>
+        <v>569</v>
       </c>
       <c r="E6" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="F6" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8972,22 +8879,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="C7" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="D7" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="E7" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="F7" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8995,22 +8902,22 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="C8" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="D8" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="E8" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="F8" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9018,22 +8925,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="C9" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="D9" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="E9" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="F9" t="s">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9041,22 +8948,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>602</v>
+        <v>587</v>
       </c>
       <c r="C10" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="D10" t="s">
+        <v>573</v>
+      </c>
+      <c r="E10" t="s">
         <v>588</v>
       </c>
-      <c r="E10" t="s">
-        <v>603</v>
-      </c>
       <c r="F10" t="s">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9064,22 +8971,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>605</v>
+        <v>590</v>
       </c>
       <c r="C11" t="s">
-        <v>606</v>
+        <v>591</v>
       </c>
       <c r="D11" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="E11" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
       <c r="F11" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -9087,22 +8994,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
       <c r="C12" t="s">
-        <v>611</v>
+        <v>596</v>
       </c>
       <c r="D12" t="s">
-        <v>612</v>
+        <v>597</v>
       </c>
       <c r="E12" t="s">
-        <v>613</v>
+        <v>598</v>
       </c>
       <c r="F12" t="s">
-        <v>614</v>
+        <v>599</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -9110,22 +9017,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>615</v>
+        <v>600</v>
       </c>
       <c r="C13" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D13" t="s">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="E13" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="F13" t="s">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -9133,22 +9040,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="C14" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="D14" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="E14" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="F14" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9156,22 +9063,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="C15" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="D15" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="E15" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="F15" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9179,22 +9086,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="C16" t="s">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="D16" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="E16" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="F16" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9202,22 +9109,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="C17" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="D17" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="E17" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="F17" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -9225,22 +9132,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>639</v>
+        <v>624</v>
       </c>
       <c r="C18" t="s">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="D18" t="s">
-        <v>641</v>
+        <v>626</v>
       </c>
       <c r="E18" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="F18" t="s">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9248,22 +9155,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="C19" t="s">
-        <v>645</v>
+        <v>630</v>
       </c>
       <c r="D19" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="E19" t="s">
-        <v>647</v>
+        <v>632</v>
       </c>
       <c r="F19" t="s">
-        <v>648</v>
+        <v>633</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -9271,22 +9178,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="C20" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="D20" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
       <c r="E20" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="F20" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -9294,22 +9201,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>651</v>
+        <v>636</v>
       </c>
       <c r="C21" t="s">
-        <v>652</v>
+        <v>637</v>
       </c>
       <c r="D21" t="s">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="E21" t="s">
-        <v>654</v>
+        <v>639</v>
       </c>
       <c r="F21" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
   </sheetData>
@@ -9332,30 +9239,30 @@
     <col min="4" max="4" width="81.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="70.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="61.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -9363,22 +9270,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>656</v>
+        <v>641</v>
       </c>
       <c r="C2" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="D2" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="E2" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="F2" t="s">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9386,22 +9293,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
       <c r="C3" t="s">
-        <v>662</v>
+        <v>647</v>
       </c>
       <c r="D3" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="E3" t="s">
-        <v>664</v>
+        <v>649</v>
       </c>
       <c r="F3" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9409,22 +9316,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="C4" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="D4" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="E4" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="F4" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -9432,22 +9339,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="C5" t="s">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="D5" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="E5" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="F5" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9455,22 +9362,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="C6" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="D6" t="s">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="E6" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="F6" t="s">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9478,22 +9385,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>681</v>
+        <v>666</v>
       </c>
       <c r="C7" t="s">
-        <v>682</v>
+        <v>667</v>
       </c>
       <c r="D7" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="E7" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="F7" t="s">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -9501,22 +9408,22 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="C8" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="D8" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="E8" t="s">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="F8" t="s">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9524,22 +9431,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>691</v>
+        <v>676</v>
       </c>
       <c r="C9" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="D9" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="E9" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="F9" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9547,22 +9454,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="C10" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="D10" t="s">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="E10" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="F10" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9570,22 +9477,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="C11" t="s">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="D11" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="E11" t="s">
-        <v>704</v>
+        <v>689</v>
       </c>
       <c r="F11" t="s">
-        <v>705</v>
+        <v>690</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -9593,22 +9500,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>706</v>
+        <v>691</v>
       </c>
       <c r="C12" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="D12" t="s">
-        <v>708</v>
+        <v>693</v>
       </c>
       <c r="E12" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="F12" t="s">
-        <v>710</v>
+        <v>695</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -9616,22 +9523,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>711</v>
+        <v>696</v>
       </c>
       <c r="C13" t="s">
-        <v>712</v>
+        <v>697</v>
       </c>
       <c r="D13" t="s">
-        <v>713</v>
+        <v>698</v>
       </c>
       <c r="E13" t="s">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="F13" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -9639,22 +9546,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="C14" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="D14" t="s">
-        <v>718</v>
+        <v>703</v>
       </c>
       <c r="E14" t="s">
-        <v>719</v>
+        <v>704</v>
       </c>
       <c r="F14" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9662,22 +9569,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="C15" t="s">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="D15" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="E15" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="F15" t="s">
-        <v>725</v>
+        <v>710</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9685,22 +9592,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="C16" t="s">
         <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="E16" t="s">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="F16" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9708,22 +9615,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="C17" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="D17" t="s">
-        <v>732</v>
+        <v>717</v>
       </c>
       <c r="E17" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
       <c r="F17" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -9731,22 +9638,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="C18" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="D18" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="E18" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
       <c r="F18" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9754,22 +9661,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
       <c r="C19" t="s">
-        <v>741</v>
+        <v>726</v>
       </c>
       <c r="D19" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
       <c r="E19" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
       <c r="F19" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -9777,22 +9684,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="C20" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="D20" t="s">
-        <v>747</v>
+        <v>732</v>
       </c>
       <c r="E20" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
       <c r="F20" t="s">
-        <v>749</v>
+        <v>734</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -9800,22 +9707,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="C21" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="D21" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="E21" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="F21" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
   </sheetData>
@@ -9841,25 +9748,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B1" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C1" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="D1" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="E1" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="G1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -9867,22 +9774,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="C2" t="s">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="D2" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="E2" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="F2" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9890,22 +9797,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>760</v>
+        <v>745</v>
       </c>
       <c r="C3" t="s">
-        <v>761</v>
+        <v>746</v>
       </c>
       <c r="D3" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="E3" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="F3" t="s">
-        <v>764</v>
+        <v>749</v>
       </c>
       <c r="G3" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9913,22 +9820,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="C4" t="s">
-        <v>766</v>
+        <v>751</v>
       </c>
       <c r="D4" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="E4" t="s">
-        <v>768</v>
+        <v>753</v>
       </c>
       <c r="F4" t="s">
-        <v>769</v>
+        <v>754</v>
       </c>
       <c r="G4" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -9936,22 +9843,22 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="C5" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="D5" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="E5" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="F5" t="s">
-        <v>774</v>
+        <v>759</v>
       </c>
       <c r="G5" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9959,22 +9866,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
       <c r="C6" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="D6" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="E6" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="F6" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9982,22 +9889,22 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="C7" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="D7" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="E7" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="F7" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="G7" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -10005,22 +9912,22 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="C8" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="D8" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="E8" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="F8" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="G8" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -10028,22 +9935,22 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="C9" t="s">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="D9" t="s">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="E9" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="F9" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="G9" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -10051,22 +9958,22 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="C10" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="D10" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="E10" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
       <c r="F10" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="G10" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -10074,22 +9981,22 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="C11" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="D11" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="E11" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="F11" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="G11" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -10097,22 +10004,22 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="C12" t="s">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="D12" t="s">
-        <v>804</v>
+        <v>789</v>
       </c>
       <c r="E12" t="s">
-        <v>805</v>
+        <v>790</v>
       </c>
       <c r="F12" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -10120,22 +10027,22 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="C13" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="D13" t="s">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="E13" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="F13" t="s">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="G13" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -10143,22 +10050,22 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="C14" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="D14" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="E14" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="F14" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="G14" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -10166,22 +10073,22 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="C15" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="D15" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="E15" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="F15" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G15" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -10189,22 +10096,22 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="C16" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D16" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="E16" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="F16" t="s">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="G16" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -10212,22 +10119,22 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>826</v>
+        <v>811</v>
       </c>
       <c r="C17" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="D17" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="E17" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="F17" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
       <c r="G17" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -10235,22 +10142,22 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>829</v>
+        <v>814</v>
       </c>
       <c r="C18" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="D18" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="E18" t="s">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="F18" t="s">
-        <v>830</v>
+        <v>815</v>
       </c>
       <c r="G18" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -10258,22 +10165,22 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C19" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="D19" t="s">
+        <v>771</v>
+      </c>
+      <c r="E19" t="s">
+        <v>815</v>
+      </c>
+      <c r="F19" t="s">
         <v>786</v>
       </c>
-      <c r="E19" t="s">
-        <v>830</v>
-      </c>
-      <c r="F19" t="s">
-        <v>801</v>
-      </c>
       <c r="G19" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -10281,22 +10188,22 @@
         <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="C20" t="s">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="D20" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="E20" t="s">
-        <v>834</v>
+        <v>819</v>
       </c>
       <c r="F20" t="s">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="G20" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -10304,22 +10211,22 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="C21" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="D21" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E21" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
       <c r="F21" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="G21" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
   </sheetData>
